--- a/副本焊缝统计R3_auto(1).xlsx
+++ b/副本焊缝统计R3_auto(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hanf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35DADACE-1ED1-466A-A574-927A1FBADE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4949FFDA-A91F-450D-BA41-C4334EFB09E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-12890" yWindow="0" windowWidth="12980" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2531" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2531" uniqueCount="89">
   <si>
     <t>序号</t>
   </si>
@@ -326,6 +326,10 @@
   </si>
   <si>
     <t>零件1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>p102</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -5133,7 +5137,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A192" s="5">
         <v>193</v>
       </c>
@@ -5147,7 +5151,7 @@
         <v>90.5</v>
       </c>
       <c r="F192" s="5" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="G192" s="5" t="s">
         <v>57</v>
@@ -5156,7 +5160,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A193" s="5">
         <v>194</v>
       </c>
@@ -5170,7 +5174,7 @@
         <v>90.5</v>
       </c>
       <c r="F193" s="5" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="G193" s="5" t="s">
         <v>57</v>
@@ -5225,7 +5229,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A196" s="5">
         <v>199</v>
       </c>
@@ -5239,7 +5243,7 @@
         <v>90.5</v>
       </c>
       <c r="F196" s="5" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="G196" s="5" t="s">
         <v>58</v>
@@ -5248,7 +5252,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A197" s="5">
         <v>200</v>
       </c>
@@ -5262,7 +5266,7 @@
         <v>90.5</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="G197" s="5" t="s">
         <v>58</v>
@@ -6559,7 +6563,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="254" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A254" s="5">
         <v>395</v>
       </c>
@@ -6582,7 +6586,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="255" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A255" s="5">
         <v>396</v>
       </c>
@@ -6605,7 +6609,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="256" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A256" s="5">
         <v>397</v>
       </c>
@@ -6628,7 +6632,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="257" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A257" s="5">
         <v>398</v>
       </c>
@@ -6651,7 +6655,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="258" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A258" s="5">
         <v>399</v>
       </c>
@@ -6674,7 +6678,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="259" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A259" s="5">
         <v>400</v>
       </c>
@@ -6697,7 +6701,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="260" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A260" s="5">
         <v>401</v>
       </c>
@@ -6720,7 +6724,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="261" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A261" s="5">
         <v>402</v>
       </c>
@@ -6743,7 +6747,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="262" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A262" s="5">
         <v>403</v>
       </c>
@@ -6766,7 +6770,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="263" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A263" s="5">
         <v>404</v>
       </c>
@@ -6789,7 +6793,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="264" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A264" s="5">
         <v>405</v>
       </c>
@@ -6812,7 +6816,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="265" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A265" s="5">
         <v>406</v>
       </c>
@@ -6835,7 +6839,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="266" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A266" s="5">
         <v>407</v>
       </c>
@@ -6858,7 +6862,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="267" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A267" s="5">
         <v>408</v>
       </c>
@@ -6881,7 +6885,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="268" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A268" s="5">
         <v>409</v>
       </c>
@@ -6904,7 +6908,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="269" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A269" s="5">
         <v>410</v>
       </c>
@@ -6927,7 +6931,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="270" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A270" s="5">
         <v>411</v>
       </c>
@@ -6950,7 +6954,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="271" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A271" s="5">
         <v>412</v>
       </c>
@@ -6973,7 +6977,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="272" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A272" s="5">
         <v>413</v>
       </c>
@@ -6996,7 +7000,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A273" s="5">
         <v>414</v>
       </c>
@@ -7019,7 +7023,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A274" s="5">
         <v>415</v>
       </c>
@@ -7042,7 +7046,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A275" s="5">
         <v>416</v>
       </c>
@@ -7065,7 +7069,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A276" s="5">
         <v>417</v>
       </c>
@@ -7088,7 +7092,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A277" s="5">
         <v>418</v>
       </c>
@@ -7111,7 +7115,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A278" s="5">
         <v>291</v>
       </c>
@@ -7134,7 +7138,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A279" s="5">
         <v>292</v>
       </c>
@@ -7157,7 +7161,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A280" s="5">
         <v>297</v>
       </c>
@@ -7180,7 +7184,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A281" s="5">
         <v>298</v>
       </c>
@@ -7203,7 +7207,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A282" s="5">
         <v>303</v>
       </c>
@@ -7226,7 +7230,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A283" s="5">
         <v>304</v>
       </c>
@@ -7249,7 +7253,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A284" s="5">
         <v>309</v>
       </c>
@@ -7272,7 +7276,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A285" s="5">
         <v>310</v>
       </c>
@@ -7295,7 +7299,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A286" s="5">
         <v>319</v>
       </c>
@@ -7318,7 +7322,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A287" s="5">
         <v>320</v>
       </c>
@@ -7341,7 +7345,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A288" s="5">
         <v>325</v>
       </c>
@@ -7364,7 +7368,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="289" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A289" s="5">
         <v>326</v>
       </c>
@@ -7387,7 +7391,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="290" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A290" s="5">
         <v>333</v>
       </c>
@@ -7410,7 +7414,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="291" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A291" s="5">
         <v>334</v>
       </c>
@@ -7433,7 +7437,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="292" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A292" s="5">
         <v>339</v>
       </c>
@@ -7456,7 +7460,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="293" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A293" s="5">
         <v>340</v>
       </c>
@@ -7479,7 +7483,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="294" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A294" s="5">
         <v>347</v>
       </c>
@@ -7502,7 +7506,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="295" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A295" s="5">
         <v>348</v>
       </c>
@@ -7525,7 +7529,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="296" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A296" s="5">
         <v>353</v>
       </c>
@@ -7548,7 +7552,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="297" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A297" s="5">
         <v>354</v>
       </c>
@@ -7571,7 +7575,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="298" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A298" s="5">
         <v>357</v>
       </c>
@@ -7594,7 +7598,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="299" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A299" s="5">
         <v>358</v>
       </c>
@@ -7617,7 +7621,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="300" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A300" s="5">
         <v>363</v>
       </c>
@@ -7640,7 +7644,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="301" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A301" s="5">
         <v>364</v>
       </c>
@@ -7663,7 +7667,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="302" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A302" s="5">
         <v>259</v>
       </c>
@@ -7686,7 +7690,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="303" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A303" s="5">
         <v>260</v>
       </c>
@@ -7709,7 +7713,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="304" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A304" s="5">
         <v>263</v>
       </c>
@@ -7732,7 +7736,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="305" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A305" s="5">
         <v>264</v>
       </c>
@@ -7755,7 +7759,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="306" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A306" s="5">
         <v>265</v>
       </c>
@@ -7778,7 +7782,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="307" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A307" s="5">
         <v>266</v>
       </c>
@@ -7801,7 +7805,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="308" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A308" s="5">
         <v>269</v>
       </c>
@@ -7824,7 +7828,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="309" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A309" s="5">
         <v>270</v>
       </c>
@@ -7847,7 +7851,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="310" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A310" s="5">
         <v>271</v>
       </c>
@@ -7870,7 +7874,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="311" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A311" s="5">
         <v>272</v>
       </c>
@@ -7893,7 +7897,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="312" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A312" s="5">
         <v>275</v>
       </c>
@@ -7916,7 +7920,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="313" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A313" s="5">
         <v>276</v>
       </c>
@@ -7939,7 +7943,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="314" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A314" s="5">
         <v>277</v>
       </c>
@@ -7962,7 +7966,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="315" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A315" s="5">
         <v>278</v>
       </c>
@@ -7985,7 +7989,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="316" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A316" s="5">
         <v>281</v>
       </c>
@@ -8008,7 +8012,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="317" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A317" s="5">
         <v>282</v>
       </c>
@@ -8031,7 +8035,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="318" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A318" s="5">
         <v>283</v>
       </c>
@@ -8054,7 +8058,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="319" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A319" s="5">
         <v>284</v>
       </c>
@@ -8077,7 +8081,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="320" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A320" s="5">
         <v>287</v>
       </c>
@@ -8100,7 +8104,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="321" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A321" s="5">
         <v>288</v>
       </c>
@@ -8123,7 +8127,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="322" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A322" s="5">
         <v>289</v>
       </c>
@@ -8146,7 +8150,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="323" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A323" s="5">
         <v>290</v>
       </c>
@@ -8169,7 +8173,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="324" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A324" s="5">
         <v>293</v>
       </c>
@@ -8192,7 +8196,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="325" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A325" s="5">
         <v>294</v>
       </c>
@@ -8215,7 +8219,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="326" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A326" s="5">
         <v>295</v>
       </c>
@@ -8238,7 +8242,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="327" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A327" s="5">
         <v>296</v>
       </c>
@@ -8261,7 +8265,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="328" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A328" s="5">
         <v>299</v>
       </c>
@@ -8284,7 +8288,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="329" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A329" s="5">
         <v>300</v>
       </c>
@@ -8307,7 +8311,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="330" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A330" s="5">
         <v>301</v>
       </c>
@@ -8330,7 +8334,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="331" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A331" s="5">
         <v>302</v>
       </c>
@@ -8353,7 +8357,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="332" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A332" s="5">
         <v>305</v>
       </c>
@@ -8376,7 +8380,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="333" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A333" s="5">
         <v>306</v>
       </c>
@@ -8399,7 +8403,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="334" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A334" s="5">
         <v>307</v>
       </c>
@@ -8422,7 +8426,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="335" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A335" s="5">
         <v>308</v>
       </c>
@@ -8445,7 +8449,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="336" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A336" s="5">
         <v>311</v>
       </c>
@@ -8468,7 +8472,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A337" s="5">
         <v>312</v>
       </c>
@@ -8491,7 +8495,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A338" s="5">
         <v>315</v>
       </c>
@@ -8514,7 +8518,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A339" s="5">
         <v>316</v>
       </c>
@@ -8537,7 +8541,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A340" s="5">
         <v>321</v>
       </c>
@@ -8560,7 +8564,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A341" s="5">
         <v>322</v>
       </c>
@@ -8583,7 +8587,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A342" s="5">
         <v>329</v>
       </c>
@@ -8606,7 +8610,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A343" s="5">
         <v>330</v>
       </c>
@@ -8629,7 +8633,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A344" s="5">
         <v>335</v>
       </c>
@@ -8652,7 +8656,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A345" s="5">
         <v>336</v>
       </c>
@@ -8675,7 +8679,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A346" s="5">
         <v>343</v>
       </c>
@@ -8698,7 +8702,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A347" s="5">
         <v>344</v>
       </c>
@@ -8721,7 +8725,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A348" s="5">
         <v>349</v>
       </c>
@@ -8744,7 +8748,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A349" s="5">
         <v>350</v>
       </c>
@@ -8767,7 +8771,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A350" s="5">
         <v>355</v>
       </c>
@@ -8790,7 +8794,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A351" s="5">
         <v>356</v>
       </c>
@@ -8813,7 +8817,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A352" s="5">
         <v>359</v>
       </c>
@@ -8836,7 +8840,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="353" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A353" s="5">
         <v>360</v>
       </c>
@@ -8859,7 +8863,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="354" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A354" s="5">
         <v>361</v>
       </c>
@@ -8882,7 +8886,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="355" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A355" s="5">
         <v>362</v>
       </c>
@@ -8905,7 +8909,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="356" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A356" s="5">
         <v>365</v>
       </c>
@@ -8928,7 +8932,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="357" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A357" s="5">
         <v>366</v>
       </c>
@@ -8951,7 +8955,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="358" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A358" s="5">
         <v>367</v>
       </c>
@@ -8974,7 +8978,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="359" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A359" s="5">
         <v>368</v>
       </c>
@@ -8997,7 +9001,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="360" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A360" s="5">
         <v>371</v>
       </c>
@@ -9020,7 +9024,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="361" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A361" s="5">
         <v>372</v>
       </c>
@@ -9043,7 +9047,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="362" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A362" s="5">
         <v>373</v>
       </c>
@@ -9066,7 +9070,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="363" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A363" s="5">
         <v>374</v>
       </c>
@@ -9089,7 +9093,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="364" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A364" s="5">
         <v>377</v>
       </c>
@@ -9112,7 +9116,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="365" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A365" s="5">
         <v>378</v>
       </c>
@@ -9135,7 +9139,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="366" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A366" s="5">
         <v>379</v>
       </c>
@@ -9158,7 +9162,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="367" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A367" s="5">
         <v>380</v>
       </c>
@@ -9181,7 +9185,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="368" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A368" s="5">
         <v>383</v>
       </c>
@@ -9204,7 +9208,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="369" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A369" s="5">
         <v>384</v>
       </c>
@@ -9227,7 +9231,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="370" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A370" s="5">
         <v>385</v>
       </c>
@@ -9250,7 +9254,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="371" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A371" s="5">
         <v>386</v>
       </c>
@@ -9273,7 +9277,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="372" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A372" s="5">
         <v>389</v>
       </c>
@@ -9296,7 +9300,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="373" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A373" s="5">
         <v>390</v>
       </c>
@@ -9319,7 +9323,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="374" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A374" s="5">
         <v>313</v>
       </c>
@@ -9342,7 +9346,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="375" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A375" s="5">
         <v>314</v>
       </c>
@@ -9365,7 +9369,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="376" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A376" s="5">
         <v>327</v>
       </c>
@@ -9388,7 +9392,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="377" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A377" s="5">
         <v>328</v>
       </c>
@@ -9411,7 +9415,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="378" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A378" s="5">
         <v>341</v>
       </c>
@@ -9434,7 +9438,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="379" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A379" s="5">
         <v>342</v>
       </c>
@@ -9457,7 +9461,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="380" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A380" s="5">
         <v>261</v>
       </c>
@@ -9480,7 +9484,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="381" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A381" s="5">
         <v>262</v>
       </c>
@@ -9503,7 +9507,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="382" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A382" s="5">
         <v>267</v>
       </c>
@@ -9526,7 +9530,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="383" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A383" s="5">
         <v>268</v>
       </c>
@@ -9549,7 +9553,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="384" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A384" s="5">
         <v>273</v>
       </c>
@@ -9572,7 +9576,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A385" s="5">
         <v>274</v>
       </c>
@@ -9595,7 +9599,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A386" s="5">
         <v>279</v>
       </c>
@@ -9618,7 +9622,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A387" s="5">
         <v>280</v>
       </c>
@@ -9641,7 +9645,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A388" s="5">
         <v>285</v>
       </c>
@@ -9664,7 +9668,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A389" s="5">
         <v>286</v>
       </c>
@@ -9687,7 +9691,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A390" s="5">
         <v>369</v>
       </c>
@@ -9710,7 +9714,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A391" s="5">
         <v>370</v>
       </c>
@@ -9733,7 +9737,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A392" s="5">
         <v>375</v>
       </c>
@@ -9756,7 +9760,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A393" s="5">
         <v>376</v>
       </c>
@@ -9779,7 +9783,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A394" s="5">
         <v>381</v>
       </c>
@@ -9802,7 +9806,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A395" s="5">
         <v>382</v>
       </c>
@@ -9825,7 +9829,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A396" s="5">
         <v>387</v>
       </c>
@@ -9848,7 +9852,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="397" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A397" s="5">
         <v>388</v>
       </c>
@@ -9871,7 +9875,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="398" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A398" s="5">
         <v>255</v>
       </c>
@@ -9894,7 +9898,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A399" s="5">
         <v>256</v>
       </c>
@@ -9917,7 +9921,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="400" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A400" s="5">
         <v>317</v>
       </c>
@@ -9940,7 +9944,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A401" s="5">
         <v>318</v>
       </c>
@@ -9963,7 +9967,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A402" s="5">
         <v>323</v>
       </c>
@@ -9986,7 +9990,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A403" s="5">
         <v>324</v>
       </c>
@@ -10009,7 +10013,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="404" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A404" s="5">
         <v>331</v>
       </c>
@@ -10032,7 +10036,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A405" s="5">
         <v>332</v>
       </c>
@@ -10055,7 +10059,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A406" s="5">
         <v>337</v>
       </c>
@@ -10078,7 +10082,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A407" s="5">
         <v>338</v>
       </c>
@@ -10101,7 +10105,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A408" s="5">
         <v>345</v>
       </c>
@@ -10124,7 +10128,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A409" s="5">
         <v>346</v>
       </c>
@@ -10147,7 +10151,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A410" s="5">
         <v>351</v>
       </c>
@@ -10170,7 +10174,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="411" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A411" s="5">
         <v>352</v>
       </c>
@@ -10193,7 +10197,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A412" s="5">
         <v>391</v>
       </c>
@@ -10216,7 +10220,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A413" s="5">
         <v>392</v>
       </c>
@@ -10239,7 +10243,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="414" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A414" s="5">
         <v>393</v>
       </c>
@@ -10262,7 +10266,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A415" s="5">
         <v>394</v>
       </c>
@@ -10285,7 +10289,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A416" s="5">
         <v>253</v>
       </c>
@@ -10308,7 +10312,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="417" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="417" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A417" s="5">
         <v>254</v>
       </c>
@@ -10331,7 +10335,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="418" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="418" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A418" s="5">
         <v>257</v>
       </c>
@@ -10354,7 +10358,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="419" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="419" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A419" s="5">
         <v>258</v>
       </c>
@@ -10379,9 +10383,14 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I419" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="p100"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="7">
       <filters>
-        <filter val="CO010"/>
+        <filter val="CO008"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A184:I225">
